--- a/buffer_results_oldv/results_(stress_test)_summary/summary.xlsx
+++ b/buffer_results_oldv/results_(stress_test)_summary/summary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\buffer_results_oldv\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAD3D7B-8ED0-45D8-BD1C-3D7869504624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -407,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -638,21 +638,51 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -665,36 +695,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -722,10 +722,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1079,10 +1078,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="111" t="s">
+      <c r="A2" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="112"/>
+      <c r="B2" s="99"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -1116,10 +1115,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="111" t="s">
+      <c r="M2" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="112"/>
+      <c r="N2" s="99"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -1147,10 +1146,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="112"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -1184,10 +1183,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="111" t="s">
+      <c r="M3" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="112"/>
+      <c r="N3" s="99"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -1215,10 +1214,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="112"/>
+      <c r="B4" s="99"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1252,10 +1251,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="111" t="s">
+      <c r="M4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="112"/>
+      <c r="N4" s="99"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -1283,31 +1282,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="112"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="99"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="111" t="s">
+      <c r="M5" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="112"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="99"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1455,38 +1454,38 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="110"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="103"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="111" t="s">
+      <c r="M8" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="113"/>
-      <c r="O8" s="116"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="116"/>
-      <c r="S8" s="116"/>
-      <c r="T8" s="116"/>
-      <c r="U8" s="110"/>
+      <c r="N8" s="104"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="110"/>
+      <c r="Q8" s="110"/>
+      <c r="R8" s="110"/>
+      <c r="S8" s="110"/>
+      <c r="T8" s="110"/>
+      <c r="U8" s="103"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
+      <c r="B9" s="99"/>
       <c r="C9" s="31">
         <v>93.782740335124032</v>
       </c>
@@ -1520,10 +1519,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="111" t="s">
+      <c r="M9" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="112"/>
+      <c r="N9" s="99"/>
       <c r="O9" s="31">
         <v>3.5391983918820551</v>
       </c>
@@ -1554,7 +1553,7 @@
       <c r="A10" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="110"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="34">
         <v>93.226230330712227</v>
       </c>
@@ -1588,10 +1587,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:I10)&amp;","</f>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="111" t="s">
+      <c r="M10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="112"/>
+      <c r="N10" s="99"/>
       <c r="O10" s="34">
         <v>3.945711842949601</v>
       </c>
@@ -1619,10 +1618,10 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="112"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="34">
         <v>93.004922187908207</v>
       </c>
@@ -1656,10 +1655,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:I11)&amp;","</f>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="111" t="s">
+      <c r="M11" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="112"/>
+      <c r="N11" s="99"/>
       <c r="O11" s="34">
         <v>3.690401528555848</v>
       </c>
@@ -1687,10 +1686,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="111" t="s">
+      <c r="A12" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="112"/>
+      <c r="B12" s="99"/>
       <c r="C12" s="37">
         <v>93.123279613145442</v>
       </c>
@@ -1724,10 +1723,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="111" t="s">
+      <c r="M12" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="112"/>
+      <c r="N12" s="99"/>
       <c r="O12" s="37">
         <v>3.8088682011350912</v>
       </c>
@@ -1755,38 +1754,38 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="113"/>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="114"/>
-      <c r="F13" s="114"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="114"/>
-      <c r="I13" s="115"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="106"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="111" t="s">
+      <c r="M13" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="113"/>
-      <c r="O13" s="114"/>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="114"/>
-      <c r="R13" s="114"/>
-      <c r="S13" s="114"/>
-      <c r="T13" s="114"/>
-      <c r="U13" s="115"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="105"/>
+      <c r="R13" s="105"/>
+      <c r="S13" s="105"/>
+      <c r="T13" s="105"/>
+      <c r="U13" s="106"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="112"/>
+      <c r="B14" s="99"/>
       <c r="C14" s="31">
         <v>92.969518190757128</v>
       </c>
@@ -1820,10 +1819,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="111" t="s">
+      <c r="M14" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="112"/>
+      <c r="N14" s="99"/>
       <c r="O14" s="31">
         <v>3.3991921823554931</v>
       </c>
@@ -1854,7 +1853,7 @@
       <c r="A15" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="110"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="34">
         <v>91.898721730580135</v>
       </c>
@@ -1888,10 +1887,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:I15)&amp;","</f>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="111" t="s">
+      <c r="M15" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="112"/>
+      <c r="N15" s="99"/>
       <c r="O15" s="34">
         <v>3.190312271555559</v>
       </c>
@@ -1919,10 +1918,10 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="34">
         <v>93.044276622923505</v>
       </c>
@@ -1956,10 +1955,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:I16)&amp;","</f>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="111" t="s">
+      <c r="M16" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="112"/>
+      <c r="N16" s="99"/>
       <c r="O16" s="34">
         <v>3.72078192123604</v>
       </c>
@@ -1987,10 +1986,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="112"/>
+      <c r="B17" s="99"/>
       <c r="C17" s="37">
         <v>93.174110502686005</v>
       </c>
@@ -2024,10 +2023,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:I17)&amp;","</f>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="111" t="s">
+      <c r="M17" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="112"/>
+      <c r="N17" s="99"/>
       <c r="O17" s="37">
         <v>3.8766021792735019</v>
       </c>
@@ -2137,10 +2136,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="98" t="s">
+      <c r="A20" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="99"/>
+      <c r="B20" s="101"/>
       <c r="C20" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -2168,10 +2167,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="98" t="s">
+      <c r="M20" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="99"/>
+      <c r="N20" s="101"/>
       <c r="O20" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -2199,10 +2198,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="98" t="s">
+      <c r="A21" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="101"/>
       <c r="C21" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -2230,10 +2229,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="98" t="s">
+      <c r="M21" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="99"/>
+      <c r="N21" s="101"/>
       <c r="O21" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -2261,10 +2260,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="99"/>
+      <c r="B22" s="101"/>
       <c r="C22" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -2292,10 +2291,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="98" t="s">
+      <c r="M22" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="99"/>
+      <c r="N22" s="101"/>
       <c r="O22" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -2323,7 +2322,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="98" t="s">
+      <c r="A23" s="100" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="107"/>
@@ -2333,11 +2332,11 @@
       <c r="F23" s="107"/>
       <c r="G23" s="107"/>
       <c r="H23" s="107"/>
-      <c r="I23" s="99"/>
+      <c r="I23" s="101"/>
       <c r="J23" s="44"/>
       <c r="K23" s="44"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="98" t="s">
+      <c r="M23" s="100" t="s">
         <v>12</v>
       </c>
       <c r="N23" s="107"/>
@@ -2347,7 +2346,7 @@
       <c r="R23" s="107"/>
       <c r="S23" s="107"/>
       <c r="T23" s="107"/>
-      <c r="U23" s="99"/>
+      <c r="U23" s="101"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2483,7 +2482,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="98" t="s">
+      <c r="A26" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="107"/>
@@ -2493,11 +2492,11 @@
       <c r="F26" s="117"/>
       <c r="G26" s="117"/>
       <c r="H26" s="117"/>
-      <c r="I26" s="101"/>
+      <c r="I26" s="112"/>
       <c r="J26" s="44"/>
       <c r="K26" s="44"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="98" t="s">
+      <c r="M26" s="100" t="s">
         <v>20</v>
       </c>
       <c r="N26" s="107"/>
@@ -2507,14 +2506,14 @@
       <c r="R26" s="117"/>
       <c r="S26" s="117"/>
       <c r="T26" s="117"/>
-      <c r="U26" s="101"/>
+      <c r="U26" s="112"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="98" t="s">
+      <c r="A27" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="99"/>
+      <c r="B27" s="101"/>
       <c r="C27" s="40">
         <v>93.403798109785029</v>
       </c>
@@ -2542,10 +2541,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="98" t="s">
+      <c r="M27" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="99"/>
+      <c r="N27" s="101"/>
       <c r="O27" s="40">
         <v>3.9553866501853321</v>
       </c>
@@ -2573,10 +2572,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="99"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="43">
         <v>92.778947400409621</v>
       </c>
@@ -2604,10 +2603,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:I28)&amp;","</f>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="98" t="s">
+      <c r="M28" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="99"/>
+      <c r="N28" s="101"/>
       <c r="O28" s="43">
         <v>4.3743918396131134</v>
       </c>
@@ -2635,10 +2634,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="98" t="s">
+      <c r="A29" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="99"/>
+      <c r="B29" s="101"/>
       <c r="C29" s="43">
         <v>92.492055194421354</v>
       </c>
@@ -2666,10 +2665,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="98" t="s">
+      <c r="M29" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="99"/>
+      <c r="N29" s="101"/>
       <c r="O29" s="43">
         <v>4.0986250609792014</v>
       </c>
@@ -2697,10 +2696,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="98" t="s">
+      <c r="A30" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="99"/>
+      <c r="B30" s="101"/>
       <c r="C30" s="46">
         <v>92.657174075741665</v>
       </c>
@@ -2728,10 +2727,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:I30)&amp;","</f>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="98" t="s">
+      <c r="M30" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="99"/>
+      <c r="N30" s="101"/>
       <c r="O30" s="46">
         <v>4.2589004392769629</v>
       </c>
@@ -2759,7 +2758,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="98" t="s">
+      <c r="A31" s="100" t="s">
         <v>23</v>
       </c>
       <c r="B31" s="107"/>
@@ -2773,7 +2772,7 @@
       <c r="J31" s="44"/>
       <c r="K31" s="44"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="98" t="s">
+      <c r="M31" s="100" t="s">
         <v>23</v>
       </c>
       <c r="N31" s="107"/>
@@ -2787,10 +2786,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98" t="s">
+      <c r="A32" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="99"/>
+      <c r="B32" s="101"/>
       <c r="C32" s="40">
         <v>92.603769819293618</v>
       </c>
@@ -2818,10 +2817,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="98" t="s">
+      <c r="M32" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="99"/>
+      <c r="N32" s="101"/>
       <c r="O32" s="40">
         <v>3.708759274801273</v>
       </c>
@@ -2849,10 +2848,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="100" t="s">
+      <c r="A33" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="101"/>
+      <c r="B33" s="112"/>
       <c r="C33" s="43">
         <v>91.377634404932721</v>
       </c>
@@ -2880,10 +2879,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="98" t="s">
+      <c r="M33" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="99"/>
+      <c r="N33" s="101"/>
       <c r="O33" s="43">
         <v>3.5684194304484111</v>
       </c>
@@ -2911,10 +2910,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="98" t="s">
+      <c r="A34" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="99"/>
+      <c r="B34" s="101"/>
       <c r="C34" s="43">
         <v>92.603715202692385</v>
       </c>
@@ -2942,10 +2941,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="98" t="s">
+      <c r="M34" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N34" s="99"/>
+      <c r="N34" s="101"/>
       <c r="O34" s="43">
         <v>4.0727132923350373</v>
       </c>
@@ -2973,10 +2972,10 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="98" t="s">
+      <c r="A35" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="99"/>
+      <c r="B35" s="101"/>
       <c r="C35" s="46">
         <v>92.692685851985146</v>
       </c>
@@ -3004,10 +3003,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:I35)&amp;","</f>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="98" t="s">
+      <c r="M35" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N35" s="99"/>
+      <c r="N35" s="101"/>
       <c r="O35" s="46">
         <v>4.3508377678439567</v>
       </c>
@@ -3116,54 +3115,6 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -3172,6 +3123,54 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I7 C9:I12 C14:I17">
@@ -3589,10 +3588,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="111" t="s">
+      <c r="A2" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="112"/>
+      <c r="B2" s="99"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3626,10 +3625,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="111" t="s">
+      <c r="M2" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="112"/>
+      <c r="N2" s="99"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -3657,10 +3656,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="112"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -3694,10 +3693,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="111" t="s">
+      <c r="M3" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="112"/>
+      <c r="N3" s="99"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -3725,10 +3724,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="112"/>
+      <c r="B4" s="99"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3762,10 +3761,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="111" t="s">
+      <c r="M4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="112"/>
+      <c r="N4" s="99"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -3793,31 +3792,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="112"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="99"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="111" t="s">
+      <c r="M5" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="112"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="99"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3893,7 +3892,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="103"/>
+      <c r="A7" s="113"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3930,7 +3929,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
-      <c r="M7" s="103"/>
+      <c r="M7" s="113"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3961,7 +3960,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="103"/>
+      <c r="A8" s="113"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3998,7 +3997,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3599108412126, 93.0049510232211, 91.6796281398051, 85.4087492106333, 76.226619607436, 61.2490650149799, 49.6316519462395,</v>
       </c>
-      <c r="M8" s="103"/>
+      <c r="M8" s="113"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -4026,7 +4025,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="103"/>
+      <c r="A9" s="113"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -4063,7 +4062,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021689922347, 93.2487766618512, 92.6912718391451, 88.4524750790808, 80.8362500252309, 58.5874935480987, 46.7616127013786,</v>
       </c>
-      <c r="M9" s="103"/>
+      <c r="M9" s="113"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -4091,7 +4090,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="103"/>
+      <c r="A10" s="113"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4128,7 +4127,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3470993117011, 92.4297413184082, 91.1779802016742, 88.6094429882612, 83.8878825364695, 65.4650299743077, 53.0259200627456,</v>
       </c>
-      <c r="M10" s="103"/>
+      <c r="M10" s="113"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4156,7 +4155,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="103"/>
+      <c r="A11" s="113"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4193,7 +4192,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    90.9754236628344, 90.2025565388397, 90.1701081612586, 88.7090805283783, 86.9509395986701, 75.7928298110999, 48.1505376344086,</v>
       </c>
-      <c r="M11" s="103"/>
+      <c r="M11" s="113"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4221,7 +4220,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="103"/>
+      <c r="A12" s="113"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4258,7 +4257,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    90.2959685349066, 90.4051130776795, 90.5292433325548, 90.4642081678907, 89.370346340943, 80.4958116708045, 54.2005092316254,</v>
       </c>
-      <c r="M12" s="103"/>
+      <c r="M12" s="113"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4286,7 +4285,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="103"/>
+      <c r="A13" s="113"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4323,7 +4322,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.7571288102262, 87.2143617159318, 87.4218577438674, 87.622418879056, 86.8073858770404, 75.9010458567981, 48.2504289252791,</v>
       </c>
-      <c r="M13" s="103"/>
+      <c r="M13" s="113"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4351,7 +4350,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="104"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4388,7 +4387,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.3893805309734, 87.1366764995084, 87.1691248770895, 87.6175024582105, 86.5250737463127, 73.9160315689006, 47.1319446246652,</v>
       </c>
-      <c r="M14" s="104"/>
+      <c r="M14" s="114"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4416,38 +4415,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="115"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="106"/>
       <c r="J15" s="35"/>
       <c r="K15" s="35"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="111" t="s">
+      <c r="M15" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="113"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="116"/>
-      <c r="S15" s="116"/>
-      <c r="T15" s="116"/>
-      <c r="U15" s="110"/>
+      <c r="N15" s="104"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="110"/>
+      <c r="R15" s="110"/>
+      <c r="S15" s="110"/>
+      <c r="T15" s="110"/>
+      <c r="U15" s="103"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="52">
         <v>93.782740335124032</v>
       </c>
@@ -4481,10 +4480,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M16" s="111" t="s">
+      <c r="M16" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="112"/>
+      <c r="N16" s="99"/>
       <c r="O16" s="52">
         <v>3.5391983918820551</v>
       </c>
@@ -4515,7 +4514,7 @@
       <c r="A17" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="110"/>
+      <c r="B17" s="103"/>
       <c r="C17" s="55">
         <v>93.226230330712227</v>
       </c>
@@ -4549,10 +4548,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M17" s="111" t="s">
+      <c r="M17" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="112"/>
+      <c r="N17" s="99"/>
       <c r="O17" s="55">
         <v>3.945711842949601</v>
       </c>
@@ -4580,10 +4579,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="112"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="55">
         <v>93.004922187908207</v>
       </c>
@@ -4617,10 +4616,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M18" s="111" t="s">
+      <c r="M18" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="112"/>
+      <c r="N18" s="99"/>
       <c r="O18" s="55">
         <v>3.690401528555848</v>
       </c>
@@ -4648,10 +4647,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="111" t="s">
+      <c r="A19" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="112"/>
+      <c r="B19" s="99"/>
       <c r="C19" s="57"/>
       <c r="D19" s="58"/>
       <c r="E19" s="58"/>
@@ -4668,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="111" t="s">
+      <c r="M19" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="112"/>
+      <c r="N19" s="99"/>
       <c r="O19" s="57"/>
       <c r="P19" s="58"/>
       <c r="Q19" s="58"/>
@@ -4682,38 +4681,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="113"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="115"/>
+      <c r="B20" s="104"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="106"/>
       <c r="J20" s="35"/>
       <c r="K20" s="35"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="111" t="s">
+      <c r="M20" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="113"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="115"/>
+      <c r="N20" s="104"/>
+      <c r="O20" s="105"/>
+      <c r="P20" s="105"/>
+      <c r="Q20" s="105"/>
+      <c r="R20" s="105"/>
+      <c r="S20" s="105"/>
+      <c r="T20" s="105"/>
+      <c r="U20" s="106"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="111" t="s">
+      <c r="A21" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="112"/>
+      <c r="B21" s="99"/>
       <c r="C21" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -4747,10 +4746,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M21" s="111" t="s">
+      <c r="M21" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="112"/>
+      <c r="N21" s="99"/>
       <c r="O21" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -4781,7 +4780,7 @@
       <c r="A22" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="110"/>
+      <c r="B22" s="103"/>
       <c r="C22" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -4815,10 +4814,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M22" s="111" t="s">
+      <c r="M22" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="112"/>
+      <c r="N22" s="99"/>
       <c r="O22" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -4846,10 +4845,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="111" t="s">
+      <c r="A23" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="112"/>
+      <c r="B23" s="99"/>
       <c r="C23" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -4883,10 +4882,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M23" s="111" t="s">
+      <c r="M23" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="112"/>
+      <c r="N23" s="99"/>
       <c r="O23" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -4914,10 +4913,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="111" t="s">
+      <c r="A24" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="112"/>
+      <c r="B24" s="99"/>
       <c r="C24" s="57"/>
       <c r="D24" s="58"/>
       <c r="E24" s="58"/>
@@ -4934,10 +4933,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="111" t="s">
+      <c r="M24" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="112"/>
+      <c r="N24" s="99"/>
       <c r="O24" s="57"/>
       <c r="P24" s="58"/>
       <c r="Q24" s="58"/>
@@ -4948,38 +4947,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="111" t="s">
+      <c r="A25" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="113"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="115"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="106"/>
       <c r="J25" s="35"/>
       <c r="K25" s="35"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="111" t="s">
+      <c r="M25" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="113"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="114"/>
-      <c r="R25" s="114"/>
-      <c r="S25" s="114"/>
-      <c r="T25" s="114"/>
-      <c r="U25" s="115"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
+      <c r="Q25" s="105"/>
+      <c r="R25" s="105"/>
+      <c r="S25" s="105"/>
+      <c r="T25" s="105"/>
+      <c r="U25" s="106"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="111" t="s">
+      <c r="A26" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="112"/>
+      <c r="B26" s="99"/>
       <c r="C26">
         <v>92.697160010034693</v>
       </c>
@@ -5013,10 +5012,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    92.6971600100347, 91.1533923303835, 90.7954999610724, 88.0886685870985, 82.9429089640337, 60.844658402466, 46.037096630017,</v>
       </c>
-      <c r="M26" s="111" t="s">
+      <c r="M26" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="112"/>
+      <c r="N26" s="99"/>
       <c r="O26">
         <v>3.4672971241319281</v>
       </c>
@@ -5047,7 +5046,7 @@
       <c r="A27" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="110"/>
+      <c r="B27" s="103"/>
       <c r="C27">
         <v>89.330608396266385</v>
       </c>
@@ -5081,10 +5080,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    89.3306083962664, 87.68534906588, 87.7563416061846, 87.3726704671609, 85.1380951969019, 69.8183029264959, 45.7455052956052,</v>
       </c>
-      <c r="M27" s="111" t="s">
+      <c r="M27" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="112"/>
+      <c r="N27" s="99"/>
       <c r="O27">
         <v>2.4752750787703639</v>
       </c>
@@ -5112,10 +5111,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="112"/>
+      <c r="B28" s="99"/>
       <c r="C28">
         <v>93.512291052114051</v>
       </c>
@@ -5149,10 +5148,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.5122910521141, 91.9882063570331, 90.3373414418233, 85.2753455191365, 76.7432359564818, 58.2251172876351, 48.5361926429583,</v>
       </c>
-      <c r="M28" s="111" t="s">
+      <c r="M28" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="112"/>
+      <c r="N28" s="99"/>
       <c r="O28">
         <v>3.4388156450568661</v>
       </c>
@@ -5180,17 +5179,17 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="111" t="s">
+      <c r="A29" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="112"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="126"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
+      <c r="B29" s="99"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
       <c r="J29" s="35" cm="1">
         <f t="array" ref="J29">-SUMPRODUCT((D1:H1-C1:G1)*(C29:G29+D29:H29)/2)</f>
         <v>0</v>
@@ -5200,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="111" t="s">
+      <c r="M29" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="112"/>
+      <c r="N29" s="99"/>
       <c r="O29" s="95"/>
       <c r="P29" s="96"/>
       <c r="Q29" s="96"/>
@@ -5296,10 +5295,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98" t="s">
+      <c r="A32" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="99"/>
+      <c r="B32" s="101"/>
       <c r="C32" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -5327,10 +5326,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M32" s="98" t="s">
+      <c r="M32" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="99"/>
+      <c r="N32" s="101"/>
       <c r="O32" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -5358,10 +5357,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="98" t="s">
+      <c r="A33" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="99"/>
+      <c r="B33" s="101"/>
       <c r="C33" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -5389,10 +5388,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M33" s="98" t="s">
+      <c r="M33" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="99"/>
+      <c r="N33" s="101"/>
       <c r="O33" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -5420,10 +5419,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="98" t="s">
+      <c r="A34" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="99"/>
+      <c r="B34" s="101"/>
       <c r="C34" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -5451,10 +5450,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M34" s="98" t="s">
+      <c r="M34" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="99"/>
+      <c r="N34" s="101"/>
       <c r="O34" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -5482,7 +5481,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="98" t="s">
+      <c r="A35" s="100" t="s">
         <v>12</v>
       </c>
       <c r="B35" s="107"/>
@@ -5492,11 +5491,11 @@
       <c r="F35" s="107"/>
       <c r="G35" s="107"/>
       <c r="H35" s="107"/>
-      <c r="I35" s="99"/>
+      <c r="I35" s="101"/>
       <c r="J35" s="44"/>
       <c r="K35" s="44"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="98" t="s">
+      <c r="M35" s="100" t="s">
         <v>12</v>
       </c>
       <c r="N35" s="107"/>
@@ -5506,11 +5505,11 @@
       <c r="R35" s="107"/>
       <c r="S35" s="107"/>
       <c r="T35" s="107"/>
-      <c r="U35" s="99"/>
+      <c r="U35" s="101"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="100" t="s">
+      <c r="A36" s="111" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5543,7 +5542,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
-      <c r="M36" s="100" t="s">
+      <c r="M36" s="111" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -5576,7 +5575,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="105"/>
+      <c r="A37" s="115"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5607,7 +5606,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
-      <c r="M37" s="105"/>
+      <c r="M37" s="115"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5638,7 +5637,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="105"/>
+      <c r="A38" s="115"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5666,7 +5665,7 @@
       <c r="J38" s="44"/>
       <c r="K38" s="44"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="105"/>
+      <c r="M38" s="115"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5694,7 +5693,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="105"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5722,7 +5721,7 @@
       <c r="J39" s="44"/>
       <c r="K39" s="44"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="105"/>
+      <c r="M39" s="115"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5750,7 +5749,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="105"/>
+      <c r="A40" s="115"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5781,7 +5780,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.9883867741658, 92.0506160293868, 90.7196986761964, 88.1856869456335, 83.275334389556, 64.6854019552345, 51.0690469748012,</v>
       </c>
-      <c r="M40" s="105"/>
+      <c r="M40" s="115"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5809,7 +5808,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="105"/>
+      <c r="A41" s="115"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5837,7 +5836,7 @@
       <c r="J41" s="44"/>
       <c r="K41" s="44"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="105"/>
+      <c r="M41" s="115"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5865,7 +5864,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="105"/>
+      <c r="A42" s="115"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5893,7 +5892,7 @@
       <c r="J42" s="44"/>
       <c r="K42" s="44"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="105"/>
+      <c r="M42" s="115"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5921,7 +5920,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="105"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5952,7 +5951,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    87.2876347990493, 86.8786967506627, 87.0833631484665, 87.3002948979049, 86.5274318222157, 75.6891287758489, 46.8869070740948,</v>
       </c>
-      <c r="M43" s="105"/>
+      <c r="M43" s="115"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5980,7 +5979,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="106"/>
+      <c r="A44" s="116"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -6008,7 +6007,7 @@
       <c r="J44" s="44"/>
       <c r="K44" s="44"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="106"/>
+      <c r="M44" s="116"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -6036,7 +6035,7 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="98" t="s">
+      <c r="A45" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B45" s="107"/>
@@ -6050,7 +6049,7 @@
       <c r="J45" s="44"/>
       <c r="K45" s="44"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="98" t="s">
+      <c r="M45" s="100" t="s">
         <v>20</v>
       </c>
       <c r="N45" s="107"/>
@@ -6064,10 +6063,10 @@
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="98" t="s">
+      <c r="A46" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="99"/>
+      <c r="B46" s="101"/>
       <c r="C46" s="60">
         <v>93.403798109785029</v>
       </c>
@@ -6095,10 +6094,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M46" s="98" t="s">
+      <c r="M46" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="99"/>
+      <c r="N46" s="101"/>
       <c r="O46" s="60">
         <v>3.9553866501853321</v>
       </c>
@@ -6126,10 +6125,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="98" t="s">
+      <c r="A47" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="99"/>
+      <c r="B47" s="101"/>
       <c r="C47" s="63">
         <v>92.778947400409621</v>
       </c>
@@ -6157,10 +6156,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M47" s="98" t="s">
+      <c r="M47" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="99"/>
+      <c r="N47" s="101"/>
       <c r="O47" s="63">
         <v>4.3743918396131134</v>
       </c>
@@ -6188,10 +6187,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="98" t="s">
+      <c r="A48" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="99"/>
+      <c r="B48" s="101"/>
       <c r="C48" s="63">
         <v>92.492055194421354</v>
       </c>
@@ -6219,10 +6218,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M48" s="98" t="s">
+      <c r="M48" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="99"/>
+      <c r="N48" s="101"/>
       <c r="O48" s="63">
         <v>4.0986250609792014</v>
       </c>
@@ -6250,10 +6249,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="98" t="s">
+      <c r="A49" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="99"/>
+      <c r="B49" s="101"/>
       <c r="C49" s="65"/>
       <c r="D49" s="66"/>
       <c r="E49" s="66"/>
@@ -6264,10 +6263,10 @@
       <c r="J49" s="51"/>
       <c r="K49" s="51"/>
       <c r="L49" s="50"/>
-      <c r="M49" s="98" t="s">
+      <c r="M49" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="99"/>
+      <c r="N49" s="101"/>
       <c r="O49" s="65"/>
       <c r="P49" s="66"/>
       <c r="Q49" s="66"/>
@@ -6278,7 +6277,7 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="98" t="s">
+      <c r="A50" s="100" t="s">
         <v>23</v>
       </c>
       <c r="B50" s="107"/>
@@ -6292,7 +6291,7 @@
       <c r="J50" s="44"/>
       <c r="K50" s="44"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="98" t="s">
+      <c r="M50" s="100" t="s">
         <v>23</v>
       </c>
       <c r="N50" s="107"/>
@@ -6306,10 +6305,10 @@
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="98" t="s">
+      <c r="A51" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="99"/>
+      <c r="B51" s="101"/>
       <c r="C51" s="60">
         <v>92.603769819293618</v>
       </c>
@@ -6337,10 +6336,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M51" s="98" t="s">
+      <c r="M51" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="99"/>
+      <c r="N51" s="101"/>
       <c r="O51" s="60">
         <v>3.708759274801273</v>
       </c>
@@ -6368,10 +6367,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="100" t="s">
+      <c r="A52" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="101"/>
+      <c r="B52" s="112"/>
       <c r="C52" s="63">
         <v>91.377634404932721</v>
       </c>
@@ -6399,10 +6398,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M52" s="98" t="s">
+      <c r="M52" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="99"/>
+      <c r="N52" s="101"/>
       <c r="O52" s="63">
         <v>3.5684194304484111</v>
       </c>
@@ -6430,10 +6429,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="98" t="s">
+      <c r="A53" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="99"/>
+      <c r="B53" s="101"/>
       <c r="C53" s="63">
         <v>92.603715202692385</v>
       </c>
@@ -6461,10 +6460,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M53" s="98" t="s">
+      <c r="M53" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="99"/>
+      <c r="N53" s="101"/>
       <c r="O53" s="63">
         <v>4.0727132923350373</v>
       </c>
@@ -6492,10 +6491,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="98" t="s">
+      <c r="A54" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="99"/>
+      <c r="B54" s="101"/>
       <c r="C54" s="65"/>
       <c r="D54" s="66"/>
       <c r="E54" s="66"/>
@@ -6506,10 +6505,10 @@
       <c r="J54" s="44"/>
       <c r="K54" s="44"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="98" t="s">
+      <c r="M54" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="99"/>
+      <c r="N54" s="101"/>
       <c r="O54" s="65"/>
       <c r="P54" s="66"/>
       <c r="Q54" s="66"/>
@@ -6520,7 +6519,7 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="98" t="s">
+      <c r="A55" s="100" t="s">
         <v>24</v>
       </c>
       <c r="B55" s="107"/>
@@ -6534,7 +6533,7 @@
       <c r="J55" s="44"/>
       <c r="K55" s="44"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="98" t="s">
+      <c r="M55" s="100" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="107"/>
@@ -6548,10 +6547,10 @@
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="98" t="s">
+      <c r="A56" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="99"/>
+      <c r="B56" s="101"/>
       <c r="C56">
         <v>92.331949706603581</v>
       </c>
@@ -6579,10 +6578,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    92.3319497066036, 90.7880554581446, 90.424281694963, 87.6576318353507, 82.4130886036769, 60.2758285841472, 42.8384283130255,</v>
       </c>
-      <c r="M56" s="98" t="s">
+      <c r="M56" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="99"/>
+      <c r="N56" s="101"/>
       <c r="O56">
         <v>3.7810235401562768</v>
       </c>
@@ -6610,10 +6609,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="100" t="s">
+      <c r="A57" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="101"/>
+      <c r="B57" s="112"/>
       <c r="C57">
         <v>88.993366976652652</v>
       </c>
@@ -6641,10 +6640,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    88.9933669766527, 87.428157448676, 87.4913674578925, 87.0361818485097, 84.7342609893418, 69.3235588863754, 44.2242612860684,</v>
       </c>
-      <c r="M57" s="98" t="s">
+      <c r="M57" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="99"/>
+      <c r="N57" s="101"/>
       <c r="O57">
         <v>2.565679873764509</v>
       </c>
@@ -6672,10 +6671,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="98" t="s">
+      <c r="A58" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="99"/>
+      <c r="B58" s="101"/>
       <c r="C58">
         <v>93.055308133932627</v>
       </c>
@@ -6703,10 +6702,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    93.0553081339326, 91.5289437140019, 89.8826389870046, 84.6748101731773, 75.9161105611017, 56.7642009645372, 44.2995900317376,</v>
       </c>
-      <c r="M58" s="98" t="s">
+      <c r="M58" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="99"/>
+      <c r="N58" s="101"/>
       <c r="O58">
         <v>3.8419168644869521</v>
       </c>
@@ -6734,10 +6733,10 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="98" t="s">
+      <c r="A59" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="99"/>
+      <c r="B59" s="101"/>
       <c r="C59" s="92"/>
       <c r="D59" s="93"/>
       <c r="E59" s="93"/>
@@ -6748,10 +6747,10 @@
       <c r="J59" s="44"/>
       <c r="K59" s="44"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="98" t="s">
+      <c r="M59" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="99"/>
+      <c r="N59" s="101"/>
       <c r="O59" s="92"/>
       <c r="P59" s="93"/>
       <c r="Q59" s="93"/>
@@ -6777,6 +6776,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="M6:M14"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="M36:M44"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="M55:U55"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M25:U25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A32:B32"/>
@@ -6793,70 +6856,6 @@
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="M6:M14"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="M36:M44"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="M55:U55"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M25:U25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
